--- a/tools/importer/reports/import-article-full.report.xlsx
+++ b/tools/importer/reports/import-article-full.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T03:18:55.011Z</t>
+    <t>2026-09-29T04:46:35.577Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:03.033Z</t>
+    <t>2026-09-29T04:46:45.639Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:16.392Z</t>
+    <t>2026-09-29T04:47:00.105Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T03:51:05.157Z</t>
+    <t>2026-09-29T04:48:31.038Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:42.140Z</t>
+    <t>2026-09-29T04:47:18.316Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:30.980Z</t>
+    <t>2026-09-29T04:47:06.080Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:36.448Z</t>
+    <t>2026-09-29T04:47:12.522Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:49.230Z</t>
+    <t>2026-09-29T04:47:24.688Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T03:19:09.164Z</t>
+    <t>2026-09-29T04:46:54.364Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T03:20:14.137Z</t>
+    <t>2026-09-29T04:48:19.394Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>

--- a/tools/importer/reports/import-article-full.report.xlsx
+++ b/tools/importer/reports/import-article-full.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T04:46:35.577Z</t>
+    <t>2026-09-29T05:48:27.130Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T04:46:45.639Z</t>
+    <t>2026-09-29T05:48:36.788Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T04:47:00.105Z</t>
+    <t>2026-09-29T05:48:49.691Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T04:48:31.038Z</t>
+    <t>2026-09-29T05:50:12.484Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T04:47:18.316Z</t>
+    <t>2026-09-29T05:49:08.031Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T04:47:06.080Z</t>
+    <t>2026-09-29T05:48:56.720Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T04:47:12.522Z</t>
+    <t>2026-09-29T05:49:02.558Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T04:47:24.688Z</t>
+    <t>2026-09-29T05:49:15.737Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T04:46:54.364Z</t>
+    <t>2026-09-29T05:48:42.473Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T04:48:19.394Z</t>
+    <t>2026-09-29T05:50:00.592Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>

--- a/tools/importer/reports/import-article-full.report.xlsx
+++ b/tools/importer/reports/import-article-full.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:27.130Z</t>
+    <t>2026-09-29T06:18:51.603Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:36.788Z</t>
+    <t>2026-09-29T06:19:01.849Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:49.691Z</t>
+    <t>2026-09-29T06:19:15.244Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T05:50:12.484Z</t>
+    <t>2026-09-29T06:20:38.591Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T05:49:08.031Z</t>
+    <t>2026-09-29T06:19:34.740Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:56.720Z</t>
+    <t>2026-09-29T06:19:22.039Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T05:49:02.558Z</t>
+    <t>2026-09-29T06:19:28.613Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T05:49:15.737Z</t>
+    <t>2026-09-29T06:19:42.918Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T05:48:42.473Z</t>
+    <t>2026-09-29T06:19:09.443Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T05:50:00.592Z</t>
+    <t>2026-09-29T06:20:27.992Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>

--- a/tools/importer/reports/import-article-full.report.xlsx
+++ b/tools/importer/reports/import-article-full.report.xlsx
@@ -67,7 +67,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-29T06:18:51.603Z</t>
+    <t>2026-09-29T06:45:35.294Z</t>
   </si>
   <si>
     <t>EMA: Department of Conservation</t>
@@ -94,7 +94,7 @@
     <t>article-hero</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:01.849Z</t>
+    <t>2026-09-29T06:45:44.683Z</t>
   </si>
   <si>
     <t>EMA: Bird flu updates: Issues</t>
@@ -115,7 +115,7 @@
     <t>The Conservation Amendment Bill aims to modernise the way conservation land is managed, support economic growth, and deliver stronger conservation outcomes.</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:15.244Z</t>
+    <t>2026-09-29T06:45:57.265Z</t>
   </si>
   <si>
     <t>EMA: Conservation Amendment Bill: Managing conservation</t>
@@ -142,7 +142,7 @@
     <t>article-full</t>
   </si>
   <si>
-    <t>2026-09-29T06:20:38.591Z</t>
+    <t>2026-09-29T06:46:56.757Z</t>
   </si>
   <si>
     <t>EMA: National Wild Goat Hunting Competition 2026</t>
@@ -166,7 +166,7 @@
     <t>A four-wheel drive (4WD) club has joined forces with the Department of Conservation to fund and plant native shrubs and trees to help cover damage done by vehicles.</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:34.740Z</t>
+    <t>2026-09-29T06:46:18.512Z</t>
   </si>
   <si>
     <t>EMA: 4WD group plants native trees to fix damage</t>
@@ -184,7 +184,7 @@
     <t>The government is boosting support for wildlife care facilities because of their key role in New Zealand’s bird flu surveillance and response, Conservation Minister Tama Potaka and Biosecurity Minister Andrew Hoggard say.</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:22.039Z</t>
+    <t>2026-09-29T06:46:04.445Z</t>
   </si>
   <si>
     <t>EMA: Funding boost for bird flu surveillance: Media release 24 September 2026</t>
@@ -205,7 +205,7 @@
     <t>The Government is taking a practical step to address contaminated sites on Crown-owned land.</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:28.613Z</t>
+    <t>2026-09-29T06:46:11.347Z</t>
   </si>
   <si>
     <t>EMA: Government invests in cleaning up contaminated Crown land: Media release 23 September 2026</t>
@@ -226,7 +226,7 @@
     <t>DOC has confirmed toxoplasmosis was the cause of death of a pregnant Hector’s dolphin found at Invercargill’s Oreti Beach last month.</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:42.918Z</t>
+    <t>2026-09-29T06:46:24.308Z</t>
   </si>
   <si>
     <t>EMA: Toxoplasmosis confirmed as cause of death of pregnant Hector’s dolphin: Media release 22 September 2026</t>
@@ -247,7 +247,7 @@
     <t>The whitebait fishing season is open. Find out when, where and how to fish for whitebait in New Zealand and the Chatham Islands.</t>
   </si>
   <si>
-    <t>2026-09-29T06:19:09.443Z</t>
+    <t>2026-09-29T06:45:51.164Z</t>
   </si>
   <si>
     <t>EMA: Whitebaiting: Things to do</t>
@@ -271,7 +271,7 @@
     <t>Discover some of our best short walks. They’re easy to get to and great for families – there’s something for everyone.</t>
   </si>
   <si>
-    <t>2026-09-29T06:20:27.992Z</t>
+    <t>2026-09-29T06:46:46.991Z</t>
   </si>
   <si>
     <t>EMA: Short Walks: Walking and tramping</t>
